--- a/study_case_model/scenario_variables/demand_scenarios124.xlsx
+++ b/study_case_model/scenario_variables/demand_scenarios124.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25852.82053282582</v>
+        <v>14362.67807379212</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2872.535614758425</v>
+        <v>14362.67807379212</v>
       </c>
     </row>
     <row r="4">
@@ -527,16 +527,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23963.01774121611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -553,11 +553,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>23963.01774121611</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -590,16 +590,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23886.13122860416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -611,12 +611,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -637,11 +637,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5971.532807151039</v>
+        <v>17914.59842145312</v>
       </c>
     </row>
     <row r="11">
@@ -653,16 +653,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>72845.44784612038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -674,16 +674,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5971.532807151039</v>
       </c>
     </row>
     <row r="13">
@@ -695,16 +695,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5971.532807151039</v>
       </c>
     </row>
     <row r="14">
@@ -716,7 +716,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11621.92484478749</v>
+        <v>72845.44784612038</v>
       </c>
     </row>
     <row r="15">
@@ -737,7 +737,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -775,20 +775,20 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20919.57554059303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -796,20 +796,20 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2324.397282288115</v>
+        <v>11621.92484478749</v>
       </c>
     </row>
     <row r="19">
@@ -817,16 +817,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -838,20 +838,20 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36844.09611630544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -859,16 +859,16 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -884,16 +884,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="23">
@@ -905,16 +905,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24604.60837491745</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="24">
@@ -926,12 +926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -947,16 +947,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6151.152093729364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -968,7 +968,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>42957.88421097572</v>
+        <v>36844.09611630544</v>
       </c>
     </row>
     <row r="27">
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1031,16 +1031,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Aker BP ASA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14534.60016344737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1052,16 +1052,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>18453.45628118809</v>
       </c>
     </row>
     <row r="31">
@@ -1073,15 +1073,225 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6151.152093729364</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6151.152093729364</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>42957.88421097572</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>14534.60016344737</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Vår Energi ASA</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Aker BP ASA</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>0</v>
       </c>
     </row>
